--- a/analytics-mvp/rop/plan/ROP_plan_template.xlsx
+++ b/analytics-mvp/rop/plan/ROP_plan_template.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>6000000</v>
+        <v>10000000</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>80000</v>
